--- a/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va demander. Il dit : on peut ? Pas pour rire de l'autre. Maman dit : on demande. Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
+          <t>Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va demander. On peut ? Pas pour rire de l'autre. On demande. Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va demander.
+narrateur|On peut ? Pas pour rire de l'autre.
+maman|On demande.
+narrateur|Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Loïs veut une photo. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Loïs a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le téléphone. Loïs donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 narrateur|Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1506,7 @@
           <t>narrateur|Loïs veut une photo. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1678,7 @@
           <t>narrateur|Loïs a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Maman range le téléphone. Loïs donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loïs demande avant la photo</t>
+          <t>Nino demande avant la photo</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au parc, une musique de manège arrive. Nino veut une photo de la grimace de Nina. Il demande. Le téléphone reste avec maman. Ce n'est pas pour rire. Puis ils demandent pour le château de sable.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va demander. On peut ? Pas pour rire de l'autre. On demande. Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
+          <t>Une musique de manège arrive de très loin. Le toboggan est tiède sous la main. Un pigeon picore une graine. Le sac de maman attend sur le banc. Le sable du bac est un peu sec. Il coule entre les doigts. Tu as entendu le manège, Nino ? Il chante tout loin. Oui. C'est de l'autre côté du parc. En ce moment, Nino est au bac à sable. Nina est là aussi. Nina fait une grimace. Sa bouche fait un petit O. Nino rit avec elle. Encore, Nina ! Nina recommence. Nino voit le téléphone de maman. Le téléphone est dans le sac, près du banc. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Nino se tourne vers Nina. Nina, on peut ? Nina dit oui. Bravo, Nino. Tu as demandé. Tu as fait du bon travail. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nino et Nina sont près du bac. Merci, maman. De rien. Le pigeon s'envole un peu. Le sable fait un petit tas. Et le château ? On peut une photo du château ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le petit château. Nina pose un caillou sur le toit. Ce n'est pas pour rire de l'autre. C'est pour garder le bac. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lissent le sable. Il est un peu rêche. Tu donnes la main ? Oui, maman. Nino donne la main à maman. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. La musique de manège s'éloigne. Le toboggan reste tiède. Le parc sent le sable chaud. Nino laisse couler le sable. Il chatouille la paume. Tu as du sable partout ? Sur les genoux. On le secoue après. Nina pose encore un caillou. Le château a deux cailloux maintenant. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Le pigeon picore plus loin. Il a trouvé une graine. Oui. On le laisse. Le banc garde le sac de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,91 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va demander.
-narrateur|On peut ? Pas pour rire de l'autre.
+          <t>narrateur|Une musique de manège arrive de très loin.
+narrateur|Le toboggan est tiède sous la main.
+narrateur|Un pigeon picore une graine.
+narrateur|Le sac de maman attend sur le banc.
+narrateur|Le sable du bac est un peu sec.
+narrateur|Il coule entre les doigts.
+maman|Tu as entendu le manège, Nino ?
+enfant-m|Il chante tout loin.
+maman|Oui.
+maman|C'est de l'autre côté du parc.
+narrateur|En ce moment, Nino est au bac à sable.
+narrateur|Nina est là aussi.
+narrateur|Nina fait une grimace.
+narrateur|Sa bouche fait un petit O.
+narrateur|Nino rit avec elle.
+enfant-m|Encore, Nina !
+narrateur|Nina recommence.
+narrateur|Nino voit le téléphone de maman.
+narrateur|Le téléphone est dans le sac, près du banc.
+enfant-m|On peut une photo ?
 maman|On demande.
-narrateur|Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.</t>
+maman|Demander, c'est parler avant.
+maman|Une photo se fait avec un adulte.
+maman|Le téléphone reste avec l'adulte.
+maman|Ce n'est pas pour rire de l'autre.
+enfant-m|D'accord.
+narrateur|Nino se tourne vers Nina.
+enfant-m|Nina, on peut ?
+narrateur|Nina dit oui.
+maman|Bravo, Nino.
+maman|Tu as demandé.
+maman|Tu as fait du bon travail.
+narrateur|Maman prend le téléphone.
+narrateur|Le téléphone reste dans sa main.
+narrateur|Maman prend la photo.
+narrateur|Nino et Nina sont près du bac.
+enfant-m|Merci, maman.
+maman|De rien.
+narrateur|Le pigeon s'envole un peu.
+narrateur|Le sable fait un petit tas.
+enfant-m|Et le château ?
+enfant-m|On peut une photo du château ?
+maman|On demande encore.
+maman|Le téléphone reste avec moi.
+enfant-m|On peut, maman ?
+maman|Oui.
+narrateur|Maman photographie le petit château.
+narrateur|Nina pose un caillou sur le toit.
+narrateur|Ce n'est pas pour rire de l'autre.
+narrateur|C'est pour garder le bac.
+maman|Tu as demandé deux fois.
+maman|Bravo.
+enfant-m|Le téléphone est avec toi.
+maman|Oui.
+maman|Avec l'adulte.
+narrateur|Ils lissent le sable.
+narrateur|Il est un peu rêche.
+maman|Tu donnes la main ?
+enfant-m|Oui, maman.
+narrateur|Nino donne la main à maman.
+narrateur|Le téléphone reste avec l'adulte.
+maman|Vous avez demandé avant la photo.
+maman|C'est le bon geste.
+enfant-m|On demande.
+enfant-m|L'adulte a le téléphone.
+maman|Oui.
+maman|Pas pour rire de l'autre.
+narrateur|La musique de manège s'éloigne.
+narrateur|Le toboggan reste tiède.
+narrateur|Le parc sent le sable chaud.
+narrateur|Nino laisse couler le sable.
+narrateur|Il chatouille la paume.
+maman|Tu as du sable partout ?
+enfant-m|Sur les genoux.
+maman|On le secoue après.
+narrateur|Nina pose encore un caillou.
+narrateur|Le château a deux cailloux maintenant.
+maman|On a demandé avant la photo.
+enfant-m|Et le téléphone est avec toi.
+maman|Oui.
+narrateur|Le pigeon picore plus loin.
+enfant-m|Il a trouvé une graine.
+maman|Oui.
+maman|On le laisse.
+narrateur|Le banc garde le sac de maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,7 +1440,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Loïs veut une photo. Que fait-il ?</t>
+          <t>Nino veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1596,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Loïs veut une photo. Que fait-il ?</t>
+          <t>narrateur|Nino veut une photo.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1625,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Loïs a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+          <t>Nino a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Nino. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1769,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Loïs a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone.</t>
+          <t>narrateur|Nino a demandé à maman.
+narrateur|Pas pour rire de l'autre.
+narrateur|L'adulte a le téléphone.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai demandé.
+enfant-m|Le téléphone est avec toi.
+maman|Oui.
+maman|Avec l'adulte.
+maman|On demande avant une photo.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1806,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le téléphone. Loïs donne la main.</t>
+          <t>Maman range le téléphone. Nino donne la main. On va vers le banc ? Oui, maman. Nina secoue le sable de ses mains. Le pigeon est revenu un peu. Tu as demandé. C'était le bon geste. Pas pour rire de l'autre. Oui. Le château garde son caillou. Le banc attend le sac.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1946,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le téléphone. Loïs donne la main.</t>
+          <t>narrateur|Maman range le téléphone.
+narrateur|Nino donne la main.
+maman|On va vers le banc ?
+enfant-m|Oui, maman.
+narrateur|Nina secoue le sable de ses mains.
+narrateur|Le pigeon est revenu un peu.
+maman|Tu as demandé.
+maman|C'était le bon geste.
+enfant-m|Pas pour rire de l'autre.
+maman|Oui.
+narrateur|Le château garde son caillou.
+narrateur|Le banc attend le sac.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1985,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. Tu as fait du bon travail. La musique de manège s'est tue. Le parc sent le sable chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2125,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a demandé.
+enfant-m|Le téléphone est avec maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La musique de manège s'est tue.
+narrateur|Le parc sent le sable chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2191,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une musique de manège arrive de très loin. Le toboggan est tiède sous la main. Un pigeon picore une graine. Le sac de maman attend sur le banc. Le sable du bac est un peu sec. Il coule entre les doigts. Tu as entendu le manège, Nino ? Il chante tout loin. Oui. C'est de l'autre côté du parc. En ce moment, Nino est au bac à sable. Nina est là aussi. Nina fait une grimace. Sa bouche fait un petit O. Nino rit avec elle. Encore, Nina ! Nina recommence. Nino voit le téléphone de maman. Le téléphone est dans le sac, près du banc. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Nino se tourne vers Nina. Nina, on peut ? Nina dit oui. Bravo, Nino. Tu as demandé. Tu as fait du bon travail. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nino et Nina sont près du bac. Merci, maman. De rien. Le pigeon s'envole un peu. Le sable fait un petit tas. Et le château ? On peut une photo du château ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le petit château. Nina pose un caillou sur le toit. Ce n'est pas pour rire de l'autre. C'est pour garder le bac. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lissent le sable. Il est un peu rêche. Tu donnes la main ? Oui, maman. Nino donne la main à maman. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. La musique de manège s'éloigne. Le toboggan reste tiède. Le parc sent le sable chaud. Nino laisse couler le sable. Il chatouille la paume. Tu as du sable partout ? Sur les genoux. On le secoue après. Nina pose encore un caillou. Le château a deux cailloux maintenant. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Le pigeon picore plus loin. Il a trouvé une graine. Oui. On le laisse. Le banc garde le sac de maman.</t>
+          <t>Une musique de manège arrive de très loin. Le toboggan est tiède sous la main. Un pigeon picore une graine. Le sac de maman attend sur le banc. Le sable du bac est un peu sec. Il coule entre les doigts. Tu as entendu le manège, Nino ? Il chante tout loin. Oui. C'est de l'autre côté du parc. En ce moment, Nino est au bac à sable. Nina est là aussi. Nina fait une grimace. Sa bouche fait un petit O. Nino rit avec elle. Encore, Nina ! Nina recommence. Nino voit le téléphone de maman. Le téléphone est dans le sac, près du banc. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Nino se tourne vers Nina. Nina, on peut ? Nina dit oui. Bravo, Nino. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nino et Nina sont près du bac. Merci, maman. De rien. Le pigeon s'envole un peu. Le sable fait un petit tas. Et le château ? On peut une photo du château ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le petit château. Nina pose un caillou sur le toit. Ce n'est pas pour rire de l'autre. C'est pour garder le bac. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lissent le sable. Il est un peu rêche. Tu donnes la main ? Oui, maman. Nino donne la main à maman. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. La musique de manège s'éloigne. Le toboggan reste tiède. Le parc sent le sable chaud. Nino laisse couler le sable. Il chatouille la paume. Tu as du sable partout ? Sur les genoux. On le secoue après. Nina pose encore un caillou. Le château a deux cailloux maintenant. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Le pigeon picore plus loin. Il a trouvé une graine. Oui. On le laisse. Le banc garde le sac de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïs est au parc avec maman. Anaïs fait une grimace. Loïs veut une photo. Maman a le téléphone. Maman, c'est l'adulte. Loïs va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Il dit : on peut ? Pas pour rire de l'autre. Maman dit : on demande. Le téléphone photographie avec un adulte. Anaïs dit oui. Maman prend la photo. Loïs dit merci. Ce n'est pas pour rire d'Anaïs.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une musique de manège arrive de très loin. Le toboggan est tiède sous la main. Un pigeon picore une graine. Le sac de maman attend sur le banc. Le sable du bac est un peu sec. Il coule entre les doigts. Tu as entendu le manège, Nino ? Il chante tout loin. Oui. C'est de l'autre côté du parc. En ce moment, Nino est au bac à sable. Nina est là aussi. Nina fait une grimace. Sa bouche fait un petit O. Nino rit avec elle. Encore, Nina ! Nina recommence. Nino voit le téléphone de maman. Le téléphone est dans le sac, près du banc. On peut une photo ? On demande. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Nino se tourne vers Nina. Nina, on peut ? Nina dit oui. Bravo, Nino. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nino et Nina sont près du bac. Merci, maman. De rien. Le pigeon s'envole un peu. Le sable fait un petit tas. Et le château ? On peut une photo du château ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le petit château. Nina pose un caillou sur le toit. Ce n'est pas pour rire de l'autre. C'est pour garder le bac. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lissent le sable. Il est un peu rêche. Tu donnes la main ? Oui, maman. Nino donne la main à maman. Le téléphone reste avec l'adulte. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. La musique de manège s'éloigne. Le toboggan reste tiède. Le parc sent le sable chaud. Nino laisse couler le sable. Il chatouille la paume. Tu as du sable partout ? Sur les genoux. On le secoue après. Nina pose encore un caillou. Le château a deux cailloux maintenant. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Le pigeon picore plus loin. Il a trouvé une graine. Oui. On le laisse. Le banc garde le sac de maman.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1355,7 +1355,6 @@
 narrateur|Nina dit oui.
 maman|Bravo, Nino.
 maman|Tu as demandé.
-maman|Tu as fait du bon travail.
 narrateur|Maman prend le téléphone.
 narrateur|Le téléphone reste dans sa main.
 narrateur|Maman prend la photo.
@@ -1445,7 +1444,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Loïs veut une photo. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1600,7 +1599,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1625,12 +1623,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Nino. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
+          <t>Nino a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Nino. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïs a demandé à maman. Pas pour rire de l'autre. L'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt; a le téléphone.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a demandé à maman. Pas pour rire de l'autre. L'adulte a le téléphone. Bravo, Nino. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1773,7 +1771,6 @@
 narrateur|Pas pour rire de l'autre.
 narrateur|L'adulte a le téléphone.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
 enfant-m|J'ai demandé.
 enfant-m|Le téléphone est avec toi.
 maman|Oui.
@@ -1781,7 +1778,6 @@
 maman|On demande avant une photo.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1811,7 +1807,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le téléphone. Loïs donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range le téléphone. Nino donne la main. On va vers le banc ? Oui, maman. Nina secoue le sable de ses mains. Le pigeon est revenu un peu. Tu as demandé. C'était le bon geste. Pas pour rire de l'autre. Oui. Le château garde son caillou. Le banc attend le sac.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1960,7 +1956,6 @@
 narrateur|Le banc attend le sac.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1985,12 +1980,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a demandé. Le téléphone est avec maman. Bravo. Tu as fait du bon travail. La musique de manège s'est tue. Le parc sent le sable chaud. L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. La musique de manège s'est tue. Le parc sent le sable chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. La musique de manège s'est tue. Le parc sent le sable chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2128,13 +2123,10 @@
           <t>enfant-m|On a demandé.
 enfant-m|Le téléphone est avec maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|La musique de manège s'est tue.
-narrateur|Le parc sent le sable chaud.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le parc sent le sable chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2153,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2190,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loïs, Anaïs, maman</t>
+          <t>Nino, Nina, maman</t>
         </is>
       </c>
     </row>
